--- a/2024-09-20018D Source Data Ext. Fig. 8.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{986B734F-84EF-42BE-B78E-188D5BE847A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B93EAE-88AF-4C9C-B989-20DA13D0C2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2024-09-20018D Source Data Ext. Fig. 8.xlsx
+++ b/2024-09-20018D Source Data Ext. Fig. 8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\Source Data_Clean_KNIT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ytian\Desktop\To be revised\Source data\Clean version\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B93EAE-88AF-4C9C-B989-20DA13D0C2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C54A797-0C2B-4785-8056-0EA7012E49D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ext. Fig. 8c" sheetId="8" r:id="rId1"/>
@@ -27,6 +27,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -87,6 +89,9 @@
     <t>Cas9</t>
   </si>
   <si>
+    <t>KE1</t>
+  </si>
+  <si>
     <t>Ext. Fig. 8e (right)</t>
   </si>
   <si>
@@ -97,10 +102,6 @@
   </si>
   <si>
     <t>RAB11A-ACTB</t>
-  </si>
-  <si>
-    <t>KE1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -111,7 +112,7 @@
     <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="177" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -140,7 +141,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial Regular"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -237,7 +238,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -250,6 +251,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -259,23 +261,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -287,16 +291,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -578,7 +582,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.3515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -587,234 +591,242 @@
     <col min="9" max="10" width="14.46875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="8"/>
-      <c r="B2" s="17" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="10"/>
+      <c r="B2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17" t="s">
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="8" t="s">
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <v>0.41</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="15">
         <v>0.35</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="15">
         <v>0.41</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="15">
         <v>0.37</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <v>0.46</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="15">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="15">
         <v>0.09</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="15">
         <v>0.04</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="15">
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>49.1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>43</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>48.3</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="8" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16">
         <v>48.7</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>44.2</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <v>45.8</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="8" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>24.9</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>21.5</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>24.7</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="16">
         <v>16</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="16">
         <v>9.9</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="16">
         <v>11.4</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="16">
         <v>11.9</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="16">
         <v>10.5</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="16">
         <v>14.5</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41"/>
     </row>
   </sheetData>
@@ -832,216 +844,216 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.3515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="8"/>
-      <c r="B2" s="18" t="s">
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="10"/>
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="18" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="18" t="s">
+      <c r="F2" s="20"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="9" t="s">
+      <c r="I2" s="20"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="12">
         <v>0.48</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="12">
         <v>0.44</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="12">
         <v>0.48</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="12">
         <v>0.56999999999999995</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="12">
         <v>0.63</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="12">
         <v>0.86</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="12">
         <v>0.04</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="12">
         <v>0.02</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="13">
         <v>50.7</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="13">
         <v>48.1</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="13">
         <v>45.2</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="9" t="s">
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13">
         <v>15.6</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="13">
         <v>13.1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="13">
         <v>15</v>
       </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="9" t="s">
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="13">
         <v>20</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="13">
         <v>23</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="13">
         <v>22.8</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="13">
         <v>15.4</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="13">
         <v>12.8</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="13">
         <v>11.7</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="13">
         <v>14</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="13">
         <v>9.6999999999999993</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="13">
         <v>6.8</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40"/>
     </row>
   </sheetData>
@@ -1059,188 +1071,188 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.3515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="5"/>
-      <c r="B2" s="21" t="s">
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A2" s="6"/>
+      <c r="B2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21" t="s">
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="4">
         <v>94.5</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="4">
         <v>78.5</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="4">
         <v>91.7</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="8">
         <v>71.8</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="8">
         <v>91</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="8">
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="12">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4">
         <v>1.4</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="4">
         <v>2</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="4">
         <v>1.2</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="8">
         <v>0.7</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="8">
         <v>1</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="8">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>99.7</v>
+      </c>
+      <c r="C9" s="4">
+        <v>99.1</v>
+      </c>
+      <c r="D9" s="4">
+        <v>99.6</v>
+      </c>
+      <c r="E9" s="4">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="F9" s="4">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="G9" s="4">
+        <v>65.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A10" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3"/>
-      <c r="B8" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="12">
-        <v>99.7</v>
-      </c>
-      <c r="C9" s="12">
-        <v>99.1</v>
-      </c>
-      <c r="D9" s="12">
-        <v>99.6</v>
-      </c>
-      <c r="E9" s="12">
-        <v>70.599999999999994</v>
-      </c>
-      <c r="F9" s="12">
-        <v>69.099999999999994</v>
-      </c>
-      <c r="G9" s="12">
-        <v>65.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="12">
+      <c r="B10" s="4">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="4">
         <v>4.3</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="4">
         <v>3.9</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="4">
         <v>0.7</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="4">
         <v>0.2</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="4">
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35"/>
     </row>
   </sheetData>
@@ -1252,147 +1264,147 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="19.3515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="3"/>
-      <c r="B2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16" t="s">
+      <c r="B2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="12">
-        <v>1.62</v>
-      </c>
-      <c r="C3" s="12">
-        <v>2.63</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="B3" s="4">
+        <v>1.57</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.38</v>
+      </c>
+      <c r="D3" s="4">
         <v>2.56</v>
       </c>
-      <c r="E3" s="12">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F3" s="12">
-        <v>1.6</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="E3" s="4">
+        <v>1.08</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.97</v>
+      </c>
+      <c r="G3" s="4">
         <v>1.19</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="12">
-        <v>0.05</v>
-      </c>
-      <c r="C4" s="12">
-        <v>0.02</v>
-      </c>
-      <c r="D4" s="12">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.04</v>
       </c>
-      <c r="E4" s="12">
-        <v>0</v>
-      </c>
-      <c r="F4" s="12">
-        <v>0.06</v>
-      </c>
-      <c r="G4" s="12">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="D4" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="E4" s="4">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.03</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8"/>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13"/>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A26"/>
     </row>
   </sheetData>
